--- a/test/list/panjalu/sandingtaman/list_sandingtaman_1.xlsx
+++ b/test/list/panjalu/sandingtaman/list_sandingtaman_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\panjalu\sandingtaman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F553453-4761-47A2-A8B0-85CDF1394042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D1BC52-31A3-4371-A33E-0D930AEDB482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="141">
   <si>
     <t>nama</t>
   </si>
@@ -193,88 +193,262 @@
     <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
   </si>
   <si>
-    <t>2023-09-01</t>
-  </si>
-  <si>
-    <t>2023-09-02</t>
-  </si>
-  <si>
-    <t>2023-09-04</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>RAGA ANANDA</t>
-  </si>
-  <si>
-    <t>ABDUL</t>
-  </si>
-  <si>
-    <t>YAYAH</t>
-  </si>
-  <si>
-    <t>HIRO PRAYOGA ABDULLAH</t>
-  </si>
-  <si>
-    <t>ANGGA</t>
-  </si>
-  <si>
-    <t>HERMAWAN</t>
-  </si>
-  <si>
-    <t>IPAH</t>
-  </si>
-  <si>
-    <t>PAHRUL HUSAINI</t>
-  </si>
-  <si>
-    <t>JAKARIA</t>
-  </si>
-  <si>
-    <t>MARPUAH</t>
-  </si>
-  <si>
-    <t>SITI NUR FADILAH</t>
-  </si>
-  <si>
-    <t>JANA</t>
-  </si>
-  <si>
-    <t>SOLIAH</t>
-  </si>
-  <si>
-    <t>DANI AL HAMDANI</t>
-  </si>
-  <si>
-    <t>SARJA</t>
-  </si>
-  <si>
-    <t>RASWI</t>
-  </si>
-  <si>
-    <t>INOH</t>
-  </si>
-  <si>
-    <t>MUSLIHIN</t>
-  </si>
-  <si>
-    <t>USMAN</t>
-  </si>
-  <si>
-    <t>HANIAH</t>
-  </si>
-  <si>
-    <t>MUMU ABDUL MUIN</t>
-  </si>
-  <si>
-    <t>LIA WATI</t>
-  </si>
-  <si>
-    <t>MILA MUAWALIAH</t>
-  </si>
-  <si>
-    <t>MUHAMAD LUTFI AZIZ</t>
+    <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
+  </si>
+  <si>
+    <t>Kualitas jaringan telepon seluler buruk di beberapa area.</t>
+  </si>
+  <si>
+    <t>Minimnya jalur sepeda membuat sulit bagi pengendara sepeda.</t>
+  </si>
+  <si>
+    <t>kondisi jalan yang kumuh dan tidak terawat rawan-.</t>
+  </si>
+  <si>
+    <t>Kelistrikan sering terganggu akibat cuaca ekstrem.</t>
+  </si>
+  <si>
+    <t>Pembangunan trotoar yang tidak merata dan berbahaya.</t>
+  </si>
+  <si>
+    <t>Tidak ada jalur khusus transportasi umum, menyebabkan kemacetan.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat penampungan untuk hewan jalanan di jalan.</t>
+  </si>
+  <si>
+    <t>Pipa air tua sering bocor dan mengganggu pasokan air.</t>
+  </si>
+  <si>
+    <t>Keterbatasan aksesibilitas bagi penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan pendapatan dan kesenjangan sosial yang semakin lebar, menciptakan keresahan di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap layanan kesehatan berkualitas, membuat banyak orang kesulitan mendapatkan perawatan yang dibutuhkan.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja dan peluang ekonomi yang memadai, meningkatkan tingkat pengangguran dan ketidakpastian pekerjaan.</t>
+  </si>
+  <si>
+    <t>Sistem pendidikan yang tidak merata dan kurang berkualitas, menghambat kemajuan sosial dan ekonomi bagi sebagian masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>ANWAR</t>
+  </si>
+  <si>
+    <t>LINA AGUS LINDA</t>
+  </si>
+  <si>
+    <t>NINA</t>
+  </si>
+  <si>
+    <t>FANI</t>
+  </si>
+  <si>
+    <t>OLIS SOLIHAT</t>
+  </si>
+  <si>
+    <t>ELI NURHOLIPAH</t>
+  </si>
+  <si>
+    <t>AMINNUDIN AZIZ</t>
+  </si>
+  <si>
+    <t>MIFTAH FARID</t>
+  </si>
+  <si>
+    <t>MULYADI</t>
+  </si>
+  <si>
+    <t>NURHAYATI</t>
+  </si>
+  <si>
+    <t>IHAH SITI SOLIHAH</t>
+  </si>
+  <si>
+    <t>INA SURYANI</t>
+  </si>
+  <si>
+    <t>WAHYO</t>
+  </si>
+  <si>
+    <t>ERUM</t>
+  </si>
+  <si>
+    <t>TOHA</t>
+  </si>
+  <si>
+    <t>DINI NURJAKIYAH</t>
+  </si>
+  <si>
+    <t>YULIAWATI</t>
+  </si>
+  <si>
+    <t>RAHMAN</t>
+  </si>
+  <si>
+    <t>UJU JUARSIH</t>
+  </si>
+  <si>
+    <t>DENI NURFADILAH</t>
+  </si>
+  <si>
+    <t>NITA</t>
+  </si>
+  <si>
+    <t>MEILANI RAHMANIA</t>
+  </si>
+  <si>
+    <t>ROHIDIN</t>
+  </si>
+  <si>
+    <t>OOH</t>
+  </si>
+  <si>
+    <t>AURA</t>
+  </si>
+  <si>
+    <t>ADRIAN SAPUTRA</t>
+  </si>
+  <si>
+    <t>ANISA</t>
+  </si>
+  <si>
+    <t>MAYA AMALIA</t>
+  </si>
+  <si>
+    <t>EDI SUPRIADI</t>
+  </si>
+  <si>
+    <t>NUNUNG NURJANAH</t>
+  </si>
+  <si>
+    <t>MAMAT</t>
+  </si>
+  <si>
+    <t>HOLISOH</t>
+  </si>
+  <si>
+    <t>RINI ANGGRAENI</t>
+  </si>
+  <si>
+    <t>AJI FIRLIANSYAH</t>
+  </si>
+  <si>
+    <t>SANEN</t>
+  </si>
+  <si>
+    <t>CARTI</t>
+  </si>
+  <si>
+    <t>HAMDULI</t>
+  </si>
+  <si>
+    <t>SITI MASITOH</t>
+  </si>
+  <si>
+    <t>FIKRI ABDULLOH</t>
+  </si>
+  <si>
+    <t>MUHAMAD ABI RAHAYU</t>
+  </si>
+  <si>
+    <t>ARYA ALIP NURHIDAYAT</t>
+  </si>
+  <si>
+    <t>AMIR</t>
+  </si>
+  <si>
+    <t>ETI RUHAETI</t>
+  </si>
+  <si>
+    <t>RIZAL MUSTOPA</t>
+  </si>
+  <si>
+    <t>AGUNG GUMELAR</t>
+  </si>
+  <si>
+    <t>IMI</t>
+  </si>
+  <si>
+    <t>ABDUL ROHIM</t>
+  </si>
+  <si>
+    <t>TOTO</t>
+  </si>
+  <si>
+    <t>PINA RAHMATUL UMAH</t>
+  </si>
+  <si>
+    <t>AIM TRI RAMDANI</t>
+  </si>
+  <si>
+    <t>AFIFAH HUMAIRA</t>
+  </si>
+  <si>
+    <t>PRIYATNA</t>
+  </si>
+  <si>
+    <t>MAHMUD</t>
+  </si>
+  <si>
+    <t>KUSYATI</t>
+  </si>
+  <si>
+    <t>2023-10-01</t>
+  </si>
+  <si>
+    <t>2023-10-02</t>
+  </si>
+  <si>
+    <t>2023-10-03</t>
+  </si>
+  <si>
+    <t>2023-10-04</t>
+  </si>
+  <si>
+    <t>2023-10-05</t>
+  </si>
+  <si>
+    <t>2023-10-06</t>
+  </si>
+  <si>
+    <t>2023-10-07</t>
+  </si>
+  <si>
+    <t>2023-10-09</t>
   </si>
 </sst>
 </file>
@@ -656,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -697,22 +871,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Nanggela</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>010</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>012</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
@@ -727,14 +901,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Cidarma</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -742,7 +916,7 @@
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>003</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
@@ -757,22 +931,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Citaman</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>002</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>011</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
@@ -787,22 +961,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Cipicung</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>007</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>008</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
@@ -817,18 +991,18 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cidarma</v>
+        <v>Citaman</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -847,22 +1021,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Nanggela</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>002</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
@@ -877,22 +1051,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Citaman</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>005</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>013</v>
       </c>
       <c r="G8" s="4" t="str">
         <f>conf!$A$2</f>
@@ -907,22 +1081,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Citaman</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>003</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>003</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
@@ -937,22 +1111,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Citaman</v>
+        <v>Cidarma</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>011</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
@@ -967,22 +1141,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Nanggela</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>008</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
@@ -997,22 +1171,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>015</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>002</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1027,22 +1201,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Sanding</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>002</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>013</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1057,10 +1231,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
@@ -1068,11 +1242,11 @@
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>001</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1087,10 +1261,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
@@ -1098,11 +1272,11 @@
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>002</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>004</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1117,22 +1291,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Cipicung</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>009</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>010</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1147,18 +1321,18 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Citaman</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1177,22 +1351,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>013</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>014</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1207,10 +1381,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
@@ -1218,11 +1392,11 @@
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>006</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1237,22 +1411,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Karoya</v>
+        <v>Citaman</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>015</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>010</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1267,22 +1441,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sindangjaya</v>
+        <v>Nanggela</v>
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1297,22 +1471,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Cipicung</v>
+        <v>Cidarma</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>008</v>
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>009</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1327,22 +1501,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Nanggela</v>
+        <v>Karoya</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1357,22 +1531,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>006</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>001</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1387,22 +1561,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
-        <v>Sanding</v>
+        <v>Cipicung</v>
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>002</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>002</v>
       </c>
       <c r="G25" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1411,6 +1585,888 @@
       <c r="H25" t="s">
         <v>41</v>
       </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G27" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G28" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Karoya</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G29" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Nanggela</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G30" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Citaman</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G31" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sanding</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G32" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G33" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G34" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Nanggela</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G35" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sanding</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G36" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G37" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H37" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G38" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G39" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G40" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Nanggela</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G41" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H41" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G42" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Citaman</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G43" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Karoya</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G44" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Citaman</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G45" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Karoya</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G46" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G47" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G48" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Nanggela</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G49" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G50" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G51" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Karoya</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G52" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H52" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Nanggela</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G53" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Citaman</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G54" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cipicung</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G55" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Sanding</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G56" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H56" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,7),1)</f>
+        <v>Cidarma</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G57" s="4" t="str">
+        <f>conf!$A$2</f>
+        <v>Sandingtaman</v>
+      </c>
+      <c r="H57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C63" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
